--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_1_14.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_1_14.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>576855.0270668475</v>
+        <v>592173.9561957517</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>925658.2446351023</v>
+        <v>925399.3994514382</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18327269.62422517</v>
+        <v>18327015.93006068</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5476385.418116931</v>
+        <v>5476496.930703655</v>
       </c>
     </row>
     <row r="11">
@@ -646,10 +646,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -691,28 +691,28 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U2" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>102.3382270926888</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>145.4467082856154</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -773,22 +773,22 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>4.525096818297269</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -825,13 +825,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>17.55829564281241</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,13 +846,13 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>44.30348359856712</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -901,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="I5" t="n">
-        <v>90.34777433931619</v>
+        <v>200.3360962888295</v>
       </c>
       <c r="J5" t="n">
         <v>11.94928935461252</v>
@@ -928,19 +928,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -949,10 +949,10 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
     </row>
     <row r="6">
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>145.3912560091964</v>
+        <v>145.4467082856154</v>
       </c>
       <c r="D6" t="n">
         <v>147.4450655646388</v>
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1092,7 +1092,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1132,19 +1132,19 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>81.00537765493284</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1165,22 +1165,22 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S8" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>102.2970636939287</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C9" t="n">
-        <v>146.1378473354543</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>147.4450655646388</v>
+        <v>126.3585902003867</v>
       </c>
       <c r="E9" t="n">
         <v>157.6450804554009</v>
@@ -1223,7 +1223,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1299,13 +1299,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>17.55829564281241</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1402,22 +1402,22 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>102.2970636939287</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1426,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
     </row>
     <row r="12">
@@ -1460,7 +1460,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1484,13 +1484,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>200.1647286948216</v>
+        <v>29.79900896488251</v>
       </c>
       <c r="U12" t="n">
         <v>225.9413820809748</v>
@@ -1499,10 +1499,10 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W12" t="n">
-        <v>3.778505492039412</v>
+        <v>241.014288877659</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1539,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1594,28 +1594,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1651,13 +1651,13 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>109.8329184249109</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>200.1647286948216</v>
@@ -1736,10 +1736,10 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>35.40726547353844</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>110.9174757594852</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1834,19 +1834,19 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>241</v>
+        <v>212.285385643442</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1894,13 +1894,13 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>212.2728000000344</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1925,13 +1925,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0.7465913262578567</v>
@@ -1958,22 +1958,22 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>171.6831711038378</v>
+        <v>34.66067414728066</v>
       </c>
       <c r="T18" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U18" t="n">
-        <v>123.5448804713173</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2046,10 +2046,10 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>47.02492433367362</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -2068,31 +2068,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>212.272800000056</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>190.3453970742847</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -2147,22 +2147,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63.84765966576211</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2201,16 +2201,16 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.687115281373639</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2314,22 +2314,22 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>202.2821007854552</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F23" t="n">
-        <v>241</v>
+        <v>82.46119763909351</v>
       </c>
       <c r="G23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2350,13 +2350,13 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -2368,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -2396,19 +2396,19 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>55.07078856377114</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2435,22 +2435,22 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>171.6831711038378</v>
+        <v>88.46061606973221</v>
       </c>
       <c r="T24" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>47.02492433367362</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -2508,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2542,19 +2542,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>80.33470701582003</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2590,25 +2590,25 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2642,7 +2642,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
         <v>0.7465913262578567</v>
@@ -2672,25 +2672,25 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>11.5314447954234</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>148.6018302582547</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2763,10 +2763,10 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -2779,13 +2779,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>241</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>212.2728000000974</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="30">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2870,16 +2870,16 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0.7465913262578567</v>
@@ -2909,25 +2909,25 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>14.53970679326745</v>
+        <v>107.2445529780796</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -2946,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2979,10 +2979,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>44.30348359856712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3025,22 +3025,22 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3064,25 +3064,25 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>68.35854314010636</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -3095,28 +3095,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>39.56167626407046</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>35.77540571240214</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -3158,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>205.7729852034775</v>
@@ -3231,13 +3231,13 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>212.2728000001407</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1.308112018705287e-10</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3313,16 +3313,16 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y35" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="36">
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>150.3737494689905</v>
+        <v>83.40091804193491</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3392,10 +3392,10 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -3490,25 +3490,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>241</v>
+        <v>212.285385643442</v>
       </c>
       <c r="C38" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D38" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3575,13 +3575,13 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>17.32995356741117</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>25.06485607370357</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3617,13 +3617,13 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>225.9413820809748</v>
@@ -3635,10 +3635,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -3727,25 +3727,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>94.38361247268791</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3775,10 +3775,10 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -3824,10 +3824,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>71.59340081828074</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0.7465913262578567</v>
@@ -3863,19 +3863,19 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>205.6826957773044</v>
+        <v>29.05241763862477</v>
       </c>
     </row>
     <row r="43">
@@ -3936,13 +3936,13 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -3979,13 +3979,13 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>82.93709327389959</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4012,25 +4012,25 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R44" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4043,16 +4043,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>115.7580399383184</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>65.07514978881805</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -4097,19 +4097,19 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X45" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>205.6826957773044</v>
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
         <v>0</v>
@@ -4289,76 +4289,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>233.6969696969697</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K2" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L2" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M2" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N2" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O2" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P2" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q2" t="n">
-        <v>964</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="R2" t="n">
-        <v>964</v>
+        <v>802.5825927271062</v>
       </c>
       <c r="S2" t="n">
-        <v>964</v>
+        <v>591.4512093066563</v>
       </c>
       <c r="T2" t="n">
-        <v>964</v>
+        <v>366.1018663125842</v>
       </c>
       <c r="U2" t="n">
-        <v>720.5656565656566</v>
+        <v>122.6530896684842</v>
       </c>
       <c r="V2" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W2" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X2" t="n">
-        <v>477.1313131313132</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y2" t="n">
-        <v>477.1313131313132</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="3">
@@ -4368,76 +4368,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.28</v>
+        <v>964.057155510636</v>
       </c>
       <c r="C3" t="n">
-        <v>19.28</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D3" t="n">
-        <v>19.28</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E3" t="n">
-        <v>19.28</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F3" t="n">
-        <v>19.28</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G3" t="n">
-        <v>19.28</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H3" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I3" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="J3" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K3" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L3" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M3" t="n">
-        <v>383.2275600578374</v>
+        <v>257.8852890990951</v>
       </c>
       <c r="N3" t="n">
-        <v>621.8175600578375</v>
+        <v>496.4894350879775</v>
       </c>
       <c r="O3" t="n">
-        <v>781.3565223866492</v>
+        <v>735.0935810768599</v>
       </c>
       <c r="P3" t="n">
-        <v>964</v>
+        <v>917.7370586902107</v>
       </c>
       <c r="Q3" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R3" t="n">
-        <v>862.8304705528857</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S3" t="n">
-        <v>689.4131260035546</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T3" t="n">
-        <v>487.2265313623206</v>
+        <v>964.057155510636</v>
       </c>
       <c r="U3" t="n">
-        <v>259.0029130987097</v>
+        <v>964.057155510636</v>
       </c>
       <c r="V3" t="n">
-        <v>23.85080486696694</v>
+        <v>964.057155510636</v>
       </c>
       <c r="W3" t="n">
-        <v>19.28</v>
+        <v>964.057155510636</v>
       </c>
       <c r="X3" t="n">
-        <v>19.28</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Y3" t="n">
-        <v>19.28</v>
+        <v>964.057155510636</v>
       </c>
     </row>
     <row r="4">
@@ -4447,76 +4447,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I4" t="n">
-        <v>19.28</v>
+        <v>136.0777814360265</v>
       </c>
       <c r="J4" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K4" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L4" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M4" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N4" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q4" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="5">
@@ -4526,76 +4526,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>122.6103673676048</v>
+        <v>477.159602222436</v>
       </c>
       <c r="C5" t="n">
-        <v>122.6103673676048</v>
+        <v>477.159602222436</v>
       </c>
       <c r="D5" t="n">
-        <v>122.6103673676048</v>
+        <v>477.159602222436</v>
       </c>
       <c r="E5" t="n">
-        <v>122.6103673676048</v>
+        <v>477.159602222436</v>
       </c>
       <c r="F5" t="n">
-        <v>122.6103673676048</v>
+        <v>477.159602222436</v>
       </c>
       <c r="G5" t="n">
-        <v>122.6103673676048</v>
+        <v>477.159602222436</v>
       </c>
       <c r="H5" t="n">
-        <v>122.6103673676048</v>
+        <v>233.710825578336</v>
       </c>
       <c r="I5" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729607</v>
       </c>
       <c r="J5" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K5" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L5" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M5" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N5" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O5" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P5" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q5" t="n">
-        <v>953.9083846317729</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R5" t="n">
-        <v>802.5254372164702</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S5" t="n">
-        <v>591.3940537960203</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T5" t="n">
-        <v>366.0447108019482</v>
+        <v>964.057155510636</v>
       </c>
       <c r="U5" t="n">
-        <v>122.6103673676048</v>
+        <v>964.057155510636</v>
       </c>
       <c r="V5" t="n">
-        <v>122.6103673676048</v>
+        <v>964.057155510636</v>
       </c>
       <c r="W5" t="n">
-        <v>122.6103673676048</v>
+        <v>964.057155510636</v>
       </c>
       <c r="X5" t="n">
-        <v>122.6103673676048</v>
+        <v>720.608378866536</v>
       </c>
       <c r="Y5" t="n">
-        <v>122.6103673676048</v>
+        <v>477.159602222436</v>
       </c>
     </row>
     <row r="6">
@@ -4605,76 +4605,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="C6" t="n">
-        <v>817.1401454452562</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D6" t="n">
-        <v>668.2057357840049</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E6" t="n">
-        <v>508.9682807785495</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F6" t="n">
-        <v>362.4337228054344</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G6" t="n">
-        <v>223.7028973880499</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H6" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I6" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="J6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K6" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L6" t="n">
-        <v>374.6006659261865</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M6" t="n">
-        <v>613.1906659261865</v>
+        <v>234.8108274061909</v>
       </c>
       <c r="N6" t="n">
-        <v>851.7806659261865</v>
+        <v>473.4149733950733</v>
       </c>
       <c r="O6" t="n">
-        <v>894.6054414866707</v>
+        <v>712.0191193839557</v>
       </c>
       <c r="P6" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973067</v>
       </c>
       <c r="Q6" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R6" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S6" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T6" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="U6" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="V6" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="W6" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="X6" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Y6" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
     </row>
     <row r="7">
@@ -4684,76 +4684,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L7" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M7" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N7" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="8">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.28</v>
+        <v>812.6742080953333</v>
       </c>
       <c r="C8" t="n">
-        <v>19.28</v>
+        <v>812.6742080953333</v>
       </c>
       <c r="D8" t="n">
-        <v>19.28</v>
+        <v>812.6742080953333</v>
       </c>
       <c r="E8" t="n">
-        <v>19.28</v>
+        <v>812.6742080953333</v>
       </c>
       <c r="F8" t="n">
-        <v>19.28</v>
+        <v>730.8505943024718</v>
       </c>
       <c r="G8" t="n">
-        <v>19.28</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="H8" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I8" t="n">
-        <v>19.28</v>
+        <v>31.35113235729607</v>
       </c>
       <c r="J8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K8" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211349</v>
       </c>
       <c r="L8" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057935</v>
       </c>
       <c r="M8" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686976</v>
       </c>
       <c r="N8" t="n">
-        <v>725.144994565301</v>
+        <v>725.202150075937</v>
       </c>
       <c r="O8" t="n">
-        <v>874.339944707949</v>
+        <v>874.397100218585</v>
       </c>
       <c r="P8" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q8" t="n">
-        <v>953.9083846317729</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R8" t="n">
-        <v>802.5254372164702</v>
+        <v>812.6742080953333</v>
       </c>
       <c r="S8" t="n">
-        <v>591.3940537960203</v>
+        <v>812.6742080953333</v>
       </c>
       <c r="T8" t="n">
-        <v>366.0447108019482</v>
+        <v>812.6742080953333</v>
       </c>
       <c r="U8" t="n">
-        <v>122.6103673676048</v>
+        <v>812.6742080953333</v>
       </c>
       <c r="V8" t="n">
-        <v>19.28</v>
+        <v>812.6742080953333</v>
       </c>
       <c r="W8" t="n">
-        <v>19.28</v>
+        <v>812.6742080953333</v>
       </c>
       <c r="X8" t="n">
-        <v>19.28</v>
+        <v>812.6742080953333</v>
       </c>
       <c r="Y8" t="n">
-        <v>19.28</v>
+        <v>812.6742080953333</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>964</v>
+        <v>795.8418184905679</v>
       </c>
       <c r="C9" t="n">
-        <v>816.3860127924704</v>
+        <v>795.8418184905679</v>
       </c>
       <c r="D9" t="n">
-        <v>667.4516031312191</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E9" t="n">
-        <v>508.2141481257637</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F9" t="n">
-        <v>361.6795901526487</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G9" t="n">
-        <v>222.9487647352642</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H9" t="n">
-        <v>109.5796291428435</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I9" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="J9" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K9" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L9" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M9" t="n">
-        <v>234.7819638733197</v>
+        <v>234.8108274061909</v>
       </c>
       <c r="N9" t="n">
-        <v>473.3719638733197</v>
+        <v>473.4149733950733</v>
       </c>
       <c r="O9" t="n">
-        <v>711.9619638733197</v>
+        <v>712.0191193839557</v>
       </c>
       <c r="P9" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973067</v>
       </c>
       <c r="Q9" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R9" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S9" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T9" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="U9" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="V9" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="W9" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="X9" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Y9" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I10" t="n">
-        <v>19.28</v>
+        <v>136.0777814360265</v>
       </c>
       <c r="J10" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L10" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M10" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N10" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19.28</v>
+        <v>477.159602222436</v>
       </c>
       <c r="C11" t="n">
-        <v>19.28</v>
+        <v>233.710825578336</v>
       </c>
       <c r="D11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K11" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L11" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M11" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N11" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759371</v>
       </c>
       <c r="O11" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185851</v>
       </c>
       <c r="P11" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q11" t="n">
-        <v>953.9083846317729</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R11" t="n">
-        <v>802.5254372164702</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S11" t="n">
-        <v>591.3940537960203</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T11" t="n">
-        <v>366.0447108019482</v>
+        <v>964.057155510636</v>
       </c>
       <c r="U11" t="n">
-        <v>122.6103673676048</v>
+        <v>964.057155510636</v>
       </c>
       <c r="V11" t="n">
-        <v>19.28</v>
+        <v>964.057155510636</v>
       </c>
       <c r="W11" t="n">
-        <v>19.28</v>
+        <v>964.057155510636</v>
       </c>
       <c r="X11" t="n">
-        <v>19.28</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Y11" t="n">
-        <v>19.28</v>
+        <v>720.608378866536</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C12" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D12" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E12" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F12" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G12" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H12" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I12" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K12" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L12" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363992</v>
       </c>
       <c r="M12" t="n">
-        <v>613.1906659261865</v>
+        <v>374.6018090363992</v>
       </c>
       <c r="N12" t="n">
-        <v>851.7806659261865</v>
+        <v>473.4149733950733</v>
       </c>
       <c r="O12" t="n">
-        <v>894.6054414866707</v>
+        <v>712.0191193839557</v>
       </c>
       <c r="P12" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973067</v>
       </c>
       <c r="Q12" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R12" t="n">
-        <v>862.8304705528857</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T12" t="n">
-        <v>487.2265313623206</v>
+        <v>933.9571464551991</v>
       </c>
       <c r="U12" t="n">
-        <v>259.0029130987097</v>
+        <v>705.7335281915882</v>
       </c>
       <c r="V12" t="n">
-        <v>23.85080486696694</v>
+        <v>470.5814199598456</v>
       </c>
       <c r="W12" t="n">
-        <v>20.03413265278571</v>
+        <v>227.1326433157456</v>
       </c>
       <c r="X12" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y12" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D13" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E13" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F13" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G13" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H13" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I13" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L13" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M13" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N13" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>953.9083846317729</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C14" t="n">
-        <v>953.9083846317729</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D14" t="n">
-        <v>953.9083846317729</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E14" t="n">
-        <v>710.4740411974295</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F14" t="n">
-        <v>467.0396977630861</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G14" t="n">
-        <v>223.6053543287427</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H14" t="n">
-        <v>223.6053543287427</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K14" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L14" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M14" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N14" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O14" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q14" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R14" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S14" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T14" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U14" t="n">
-        <v>953.9083846317729</v>
+        <v>710.516763498309</v>
       </c>
       <c r="V14" t="n">
-        <v>953.9083846317729</v>
+        <v>710.516763498309</v>
       </c>
       <c r="W14" t="n">
-        <v>953.9083846317729</v>
+        <v>467.067986854209</v>
       </c>
       <c r="X14" t="n">
-        <v>953.9083846317729</v>
+        <v>467.067986854209</v>
       </c>
       <c r="Y14" t="n">
-        <v>953.9083846317729</v>
+        <v>467.067986854209</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K15" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L15" t="n">
-        <v>234.7819638733197</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M15" t="n">
-        <v>473.3719638733197</v>
+        <v>383.2428491569326</v>
       </c>
       <c r="N15" t="n">
-        <v>473.3719638733197</v>
+        <v>621.8469951458151</v>
       </c>
       <c r="O15" t="n">
-        <v>711.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P15" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S15" t="n">
-        <v>853.0576581566556</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T15" t="n">
-        <v>650.8710635154216</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U15" t="n">
-        <v>422.6474452518107</v>
+        <v>533.6469426057913</v>
       </c>
       <c r="V15" t="n">
-        <v>187.495337020068</v>
+        <v>298.4948343740486</v>
       </c>
       <c r="W15" t="n">
-        <v>187.495337020068</v>
+        <v>55.04605772994853</v>
       </c>
       <c r="X15" t="n">
-        <v>187.495337020068</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y15" t="n">
-        <v>187.495337020068</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F16" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G16" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H16" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I16" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J16" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K16" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L16" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M16" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N16" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C17" t="n">
-        <v>19.28</v>
+        <v>749.627473042513</v>
       </c>
       <c r="D17" t="n">
-        <v>19.28</v>
+        <v>749.627473042513</v>
       </c>
       <c r="E17" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F17" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K17" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L17" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M17" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N17" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O17" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P17" t="n">
-        <v>964.0000000000348</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q17" t="n">
-        <v>964.0000000000348</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R17" t="n">
-        <v>964.0000000000348</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S17" t="n">
-        <v>964.0000000000348</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T17" t="n">
-        <v>964.0000000000348</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U17" t="n">
-        <v>964.0000000000348</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V17" t="n">
-        <v>964.0000000000348</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W17" t="n">
-        <v>749.5830303030303</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X17" t="n">
-        <v>506.1486868686869</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y17" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>362.4337228054344</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C18" t="n">
-        <v>362.4337228054344</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D18" t="n">
-        <v>362.4337228054344</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E18" t="n">
-        <v>362.4337228054344</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F18" t="n">
-        <v>362.4337228054344</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G18" t="n">
-        <v>223.7028973880499</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H18" t="n">
-        <v>110.3337617956292</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I18" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L18" t="n">
-        <v>249.2431058683491</v>
+        <v>248.2447175439888</v>
       </c>
       <c r="M18" t="n">
-        <v>304.1765223866491</v>
+        <v>486.8488635328713</v>
       </c>
       <c r="N18" t="n">
-        <v>542.7665223866492</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O18" t="n">
-        <v>781.3565223866492</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P18" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q18" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R18" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S18" t="n">
-        <v>689.4131260035546</v>
+        <v>929.0463735436861</v>
       </c>
       <c r="T18" t="n">
-        <v>487.2265313623206</v>
+        <v>726.8597789024521</v>
       </c>
       <c r="U18" t="n">
-        <v>362.4337228054344</v>
+        <v>498.6361606388412</v>
       </c>
       <c r="V18" t="n">
-        <v>362.4337228054344</v>
+        <v>263.4840524070985</v>
       </c>
       <c r="W18" t="n">
-        <v>362.4337228054344</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="X18" t="n">
-        <v>362.4337228054344</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="Y18" t="n">
-        <v>362.4337228054344</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L19" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M19" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N19" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q19" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R19" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S19" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T19" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U19" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>506.1486868686869</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="C20" t="n">
-        <v>262.7143434343434</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="D20" t="n">
-        <v>19.28</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="E20" t="n">
-        <v>19.28</v>
+        <v>710.516763498309</v>
       </c>
       <c r="F20" t="n">
-        <v>19.28</v>
+        <v>467.067986854209</v>
       </c>
       <c r="G20" t="n">
-        <v>19.28</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964.0000000000566</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964.0000000000566</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R20" t="n">
-        <v>964.0000000000566</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S20" t="n">
-        <v>964.0000000000566</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T20" t="n">
-        <v>964.0000000000566</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U20" t="n">
-        <v>964.0000000000566</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V20" t="n">
-        <v>720.5656565657132</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W20" t="n">
-        <v>720.5656565657132</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X20" t="n">
-        <v>720.5656565657132</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="Y20" t="n">
-        <v>720.5656565657132</v>
+        <v>953.9655401424092</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.28</v>
+        <v>787.9255531013317</v>
       </c>
       <c r="C21" t="n">
-        <v>19.28</v>
+        <v>613.4725238202047</v>
       </c>
       <c r="D21" t="n">
-        <v>19.28</v>
+        <v>464.5381141589534</v>
       </c>
       <c r="E21" t="n">
-        <v>19.28</v>
+        <v>305.3006591534979</v>
       </c>
       <c r="F21" t="n">
-        <v>19.28</v>
+        <v>158.7661011803829</v>
       </c>
       <c r="G21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M21" t="n">
-        <v>249.2431058683491</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N21" t="n">
-        <v>487.8331058683492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O21" t="n">
-        <v>726.4231058683491</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P21" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>790.5826554506689</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T21" t="n">
-        <v>790.5826554506689</v>
+        <v>787.9255531013317</v>
       </c>
       <c r="U21" t="n">
-        <v>562.359037187058</v>
+        <v>787.9255531013317</v>
       </c>
       <c r="V21" t="n">
-        <v>327.2069289553153</v>
+        <v>787.9255531013317</v>
       </c>
       <c r="W21" t="n">
-        <v>83.77258552097183</v>
+        <v>787.9255531013317</v>
       </c>
       <c r="X21" t="n">
-        <v>83.77258552097183</v>
+        <v>787.9255531013317</v>
       </c>
       <c r="Y21" t="n">
-        <v>83.77258552097183</v>
+        <v>787.9255531013317</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>953.9083846317729</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="C23" t="n">
-        <v>953.9083846317729</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="D23" t="n">
-        <v>953.9083846317729</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="E23" t="n">
-        <v>749.5830303030303</v>
+        <v>114.6452713866835</v>
       </c>
       <c r="F23" t="n">
-        <v>506.1486868686869</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="G23" t="n">
-        <v>262.7143434343434</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>953.9083846317729</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S23" t="n">
-        <v>953.9083846317729</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="T23" t="n">
-        <v>953.9083846317729</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="U23" t="n">
-        <v>953.9083846317729</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="V23" t="n">
-        <v>953.9083846317729</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="W23" t="n">
-        <v>953.9083846317729</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="X23" t="n">
-        <v>953.9083846317729</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="Y23" t="n">
-        <v>953.9083846317729</v>
+        <v>358.0940480307835</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>360.1724425458239</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C24" t="n">
-        <v>360.1724425458239</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D24" t="n">
-        <v>360.1724425458239</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E24" t="n">
-        <v>360.1724425458239</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F24" t="n">
-        <v>213.6378845727089</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G24" t="n">
-        <v>74.90705915532439</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H24" t="n">
-        <v>74.90705915532439</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M24" t="n">
-        <v>487.8331058683492</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N24" t="n">
-        <v>726.4231058683491</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="O24" t="n">
-        <v>964</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>790.5826554506689</v>
+        <v>874.7029978644421</v>
       </c>
       <c r="T24" t="n">
-        <v>588.3960608094349</v>
+        <v>874.7029978644421</v>
       </c>
       <c r="U24" t="n">
-        <v>360.1724425458239</v>
+        <v>874.7029978644421</v>
       </c>
       <c r="V24" t="n">
-        <v>360.1724425458239</v>
+        <v>639.5508896326994</v>
       </c>
       <c r="W24" t="n">
-        <v>360.1724425458239</v>
+        <v>396.1021129885993</v>
       </c>
       <c r="X24" t="n">
-        <v>360.1724425458239</v>
+        <v>188.2506127830665</v>
       </c>
       <c r="Y24" t="n">
-        <v>360.1724425458239</v>
+        <v>188.2506127830665</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>66.7799235693673</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V25" t="n">
-        <v>66.7799235693673</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W25" t="n">
-        <v>66.7799235693673</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X25" t="n">
-        <v>66.7799235693673</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y25" t="n">
-        <v>66.7799235693673</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>19.28</v>
+        <v>343.8760884571613</v>
       </c>
       <c r="C26" t="n">
-        <v>19.28</v>
+        <v>343.8760884571613</v>
       </c>
       <c r="D26" t="n">
-        <v>19.28</v>
+        <v>100.4273118130612</v>
       </c>
       <c r="E26" t="n">
-        <v>19.28</v>
+        <v>100.4273118130612</v>
       </c>
       <c r="F26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S26" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="T26" t="n">
-        <v>964</v>
+        <v>587.3248651012614</v>
       </c>
       <c r="U26" t="n">
-        <v>749.5830303030303</v>
+        <v>587.3248651012614</v>
       </c>
       <c r="V26" t="n">
-        <v>506.1486868686869</v>
+        <v>587.3248651012614</v>
       </c>
       <c r="W26" t="n">
-        <v>506.1486868686869</v>
+        <v>587.3248651012614</v>
       </c>
       <c r="X26" t="n">
-        <v>262.7143434343434</v>
+        <v>343.8760884571613</v>
       </c>
       <c r="Y26" t="n">
-        <v>262.7143434343434</v>
+        <v>343.8760884571613</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>194.4871619339127</v>
+        <v>110.334904905842</v>
       </c>
       <c r="C27" t="n">
-        <v>20.03413265278571</v>
+        <v>110.334904905842</v>
       </c>
       <c r="D27" t="n">
-        <v>20.03413265278571</v>
+        <v>110.334904905842</v>
       </c>
       <c r="E27" t="n">
-        <v>20.03413265278571</v>
+        <v>110.334904905842</v>
       </c>
       <c r="F27" t="n">
-        <v>20.03413265278571</v>
+        <v>110.334904905842</v>
       </c>
       <c r="G27" t="n">
-        <v>20.03413265278571</v>
+        <v>110.334904905842</v>
       </c>
       <c r="H27" t="n">
-        <v>20.03413265278571</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L27" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M27" t="n">
-        <v>542.7665223866492</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N27" t="n">
-        <v>542.7665223866492</v>
+        <v>726.4525409563269</v>
       </c>
       <c r="O27" t="n">
-        <v>781.3565223866492</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>952.409231474855</v>
       </c>
       <c r="T27" t="n">
-        <v>964</v>
+        <v>750.222636833621</v>
       </c>
       <c r="U27" t="n">
-        <v>813.8971411532781</v>
+        <v>521.9990185700101</v>
       </c>
       <c r="V27" t="n">
-        <v>813.8971411532781</v>
+        <v>521.9990185700101</v>
       </c>
       <c r="W27" t="n">
-        <v>570.4627977189347</v>
+        <v>278.55024192591</v>
       </c>
       <c r="X27" t="n">
-        <v>570.4627977189347</v>
+        <v>278.55024192591</v>
       </c>
       <c r="Y27" t="n">
-        <v>362.7024989539808</v>
+        <v>278.55024192591</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C29" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964.0000000000985</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964.0000000000985</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R29" t="n">
-        <v>964.0000000000985</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S29" t="n">
-        <v>964.0000000000985</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T29" t="n">
-        <v>964.0000000000985</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U29" t="n">
-        <v>749.5830303030303</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V29" t="n">
-        <v>749.5830303030303</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W29" t="n">
-        <v>749.5830303030303</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X29" t="n">
-        <v>749.5830303030303</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="Y29" t="n">
-        <v>506.1486868686869</v>
+        <v>710.516763498309</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>110.3337617956292</v>
+        <v>479.7536884346249</v>
       </c>
       <c r="C30" t="n">
-        <v>110.3337617956292</v>
+        <v>305.3006591534979</v>
       </c>
       <c r="D30" t="n">
-        <v>110.3337617956292</v>
+        <v>305.3006591534979</v>
       </c>
       <c r="E30" t="n">
-        <v>110.3337617956292</v>
+        <v>305.3006591534979</v>
       </c>
       <c r="F30" t="n">
-        <v>110.3337617956292</v>
+        <v>158.7661011803829</v>
       </c>
       <c r="G30" t="n">
-        <v>110.3337617956292</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H30" t="n">
-        <v>110.3337617956292</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I30" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>374.6006659261865</v>
+        <v>234.810827406191</v>
       </c>
       <c r="M30" t="n">
-        <v>374.6006659261865</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N30" t="n">
-        <v>542.7665223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="O30" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T30" t="n">
-        <v>588.3960608094349</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U30" t="n">
-        <v>360.1724425458239</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V30" t="n">
-        <v>125.0203343140812</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W30" t="n">
-        <v>110.3337617956292</v>
+        <v>855.7293242196467</v>
       </c>
       <c r="X30" t="n">
-        <v>110.3337617956292</v>
+        <v>855.7293242196467</v>
       </c>
       <c r="Y30" t="n">
-        <v>110.3337617956292</v>
+        <v>647.9690254546929</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C31" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D31" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V31" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W31" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X31" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y31" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C32" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D32" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E32" t="n">
-        <v>31.34998924708335</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="F32" t="n">
-        <v>31.34998924708335</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="G32" t="n">
-        <v>31.34998924708335</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="H32" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R32" t="n">
-        <v>812.6170525846973</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S32" t="n">
-        <v>812.6170525846973</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T32" t="n">
-        <v>587.2677095906251</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U32" t="n">
-        <v>587.2677095906251</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V32" t="n">
-        <v>518.2186761157702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W32" t="n">
-        <v>274.7843326814268</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X32" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y32" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>268.817084148299</v>
+        <v>380.2300195200815</v>
       </c>
       <c r="C33" t="n">
-        <v>268.817084148299</v>
+        <v>205.7769902389545</v>
       </c>
       <c r="D33" t="n">
-        <v>268.817084148299</v>
+        <v>205.7769902389545</v>
       </c>
       <c r="E33" t="n">
-        <v>109.5796291428435</v>
+        <v>205.7769902389545</v>
       </c>
       <c r="F33" t="n">
-        <v>109.5796291428435</v>
+        <v>59.24243226583945</v>
       </c>
       <c r="G33" t="n">
-        <v>109.5796291428435</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H33" t="n">
-        <v>109.5796291428435</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L33" t="n">
-        <v>19.28</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M33" t="n">
-        <v>257.87</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N33" t="n">
-        <v>496.46</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O33" t="n">
-        <v>711.9619638733197</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P33" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S33" t="n">
-        <v>927.8632265531292</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T33" t="n">
-        <v>927.8632265531292</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U33" t="n">
-        <v>927.8632265531292</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V33" t="n">
-        <v>927.8632265531292</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W33" t="n">
-        <v>684.4288831187857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X33" t="n">
-        <v>476.577382913253</v>
+        <v>756.2056553051034</v>
       </c>
       <c r="Y33" t="n">
-        <v>268.817084148299</v>
+        <v>548.4453565401495</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L34" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M34" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N34" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O34" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P34" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q34" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R34" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S34" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T34" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U34" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V34" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>477.1313131314553</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C35" t="n">
-        <v>233.6969696971118</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>19.27999999986787</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>122.2950059107902</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>302.3708574954488</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>519.346484758353</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>725.2010069655923</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>874.3959571082404</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>964.0000000001421</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>964.0000000001421</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R35" t="n">
-        <v>964.0000000001421</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S35" t="n">
-        <v>964.0000000001421</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T35" t="n">
-        <v>964.0000000001421</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U35" t="n">
-        <v>964.0000000001421</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V35" t="n">
-        <v>964.0000000001421</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W35" t="n">
-        <v>964.0000000001421</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X35" t="n">
-        <v>964.0000000001421</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y35" t="n">
-        <v>720.5656565657987</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>171.1726762313035</v>
+        <v>104.2786273205085</v>
       </c>
       <c r="C36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L36" t="n">
-        <v>249.2431058683491</v>
+        <v>248.2447175439888</v>
       </c>
       <c r="M36" t="n">
-        <v>487.8331058683492</v>
+        <v>486.8488635328713</v>
       </c>
       <c r="N36" t="n">
-        <v>726.4231058683491</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S36" t="n">
-        <v>790.5826554506689</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T36" t="n">
-        <v>790.5826554506689</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="U36" t="n">
-        <v>790.5826554506689</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="V36" t="n">
-        <v>790.5826554506689</v>
+        <v>555.4877027295624</v>
       </c>
       <c r="W36" t="n">
-        <v>547.1483120163255</v>
+        <v>312.0389260854624</v>
       </c>
       <c r="X36" t="n">
-        <v>547.1483120163255</v>
+        <v>312.0389260854624</v>
       </c>
       <c r="Y36" t="n">
-        <v>339.3880132513715</v>
+        <v>104.2786273205085</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L37" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M37" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N37" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>710.4740411974295</v>
+        <v>749.627473042513</v>
       </c>
       <c r="C38" t="n">
-        <v>467.0396977630861</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D38" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E38" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F38" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="G38" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R38" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S38" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T38" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U38" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V38" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W38" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X38" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y38" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>360.1724425458239</v>
+        <v>219.0522088294242</v>
       </c>
       <c r="C39" t="n">
-        <v>185.7194132646969</v>
+        <v>44.59917954829714</v>
       </c>
       <c r="D39" t="n">
-        <v>36.78500360344563</v>
+        <v>44.59917954829714</v>
       </c>
       <c r="E39" t="n">
-        <v>19.28</v>
+        <v>44.59917954829714</v>
       </c>
       <c r="F39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L39" t="n">
-        <v>249.2431058683491</v>
+        <v>65.60123993063803</v>
       </c>
       <c r="M39" t="n">
-        <v>486.8199999999999</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N39" t="n">
-        <v>725.41</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O39" t="n">
-        <v>964</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R39" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S39" t="n">
-        <v>790.5826554506689</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T39" t="n">
-        <v>588.3960608094349</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="U39" t="n">
-        <v>360.1724425458239</v>
+        <v>634.6640077999109</v>
       </c>
       <c r="V39" t="n">
-        <v>360.1724425458239</v>
+        <v>634.6640077999109</v>
       </c>
       <c r="W39" t="n">
-        <v>360.1724425458239</v>
+        <v>634.6640077999109</v>
       </c>
       <c r="X39" t="n">
-        <v>360.1724425458239</v>
+        <v>426.8125075943781</v>
       </c>
       <c r="Y39" t="n">
-        <v>360.1724425458239</v>
+        <v>219.0522088294242</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L40" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M40" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N40" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>506.1486868686869</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C41" t="n">
-        <v>262.7143434343434</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="D41" t="n">
-        <v>19.28</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="E41" t="n">
-        <v>19.28</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="F41" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="G41" t="n">
-        <v>19.28</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="H41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K41" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L41" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M41" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N41" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O41" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P41" t="n">
-        <v>964.0000000000839</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q41" t="n">
-        <v>964.0000000000839</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R41" t="n">
-        <v>812.6170525847812</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S41" t="n">
-        <v>601.4856691643313</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T41" t="n">
-        <v>601.4856691643313</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U41" t="n">
-        <v>601.4856691643313</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V41" t="n">
-        <v>601.4856691643313</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W41" t="n">
-        <v>601.4856691643313</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X41" t="n">
-        <v>601.4856691643313</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y41" t="n">
-        <v>601.4856691643313</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>380.1728640094453</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C42" t="n">
-        <v>205.7198347283183</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D42" t="n">
-        <v>205.7198347283183</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E42" t="n">
-        <v>205.7198347283183</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F42" t="n">
-        <v>205.7198347283183</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G42" t="n">
-        <v>205.7198347283183</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H42" t="n">
-        <v>92.35069913589759</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I42" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K42" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L42" t="n">
-        <v>374.6006659261865</v>
+        <v>248.2447175439888</v>
       </c>
       <c r="M42" t="n">
-        <v>613.1906659261865</v>
+        <v>486.8488635328713</v>
       </c>
       <c r="N42" t="n">
-        <v>851.7806659261865</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O42" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P42" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U42" t="n">
-        <v>964</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V42" t="n">
-        <v>964</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W42" t="n">
-        <v>964</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="X42" t="n">
-        <v>756.1484997944672</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="Y42" t="n">
-        <v>548.3882010295133</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L43" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M43" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N43" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S43" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T43" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="44">
@@ -7607,76 +7607,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>559.0910937821268</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C44" t="n">
-        <v>559.0910937821268</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D44" t="n">
-        <v>559.0910937821268</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E44" t="n">
-        <v>559.0910937821268</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F44" t="n">
-        <v>559.0910937821268</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G44" t="n">
-        <v>315.6567503477834</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H44" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K44" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L44" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M44" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N44" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O44" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P44" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q44" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R44" t="n">
-        <v>802.5254372164702</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S44" t="n">
-        <v>802.5254372164702</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T44" t="n">
-        <v>802.5254372164702</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U44" t="n">
-        <v>802.5254372164702</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V44" t="n">
-        <v>802.5254372164702</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="W44" t="n">
-        <v>559.0910937821268</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X44" t="n">
-        <v>559.0910937821268</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y44" t="n">
-        <v>559.0910937821268</v>
+        <v>262.7299197543128</v>
       </c>
     </row>
     <row r="45">
@@ -7686,76 +7686,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>85.01247453415965</v>
+        <v>193.7341723913397</v>
       </c>
       <c r="C45" t="n">
-        <v>85.01247453415965</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D45" t="n">
-        <v>85.01247453415965</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K45" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L45" t="n">
-        <v>374.6006659261865</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M45" t="n">
-        <v>613.1906659261865</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N45" t="n">
-        <v>851.7806659261865</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O45" t="n">
-        <v>894.6054414866707</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P45" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T45" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U45" t="n">
-        <v>735.7763817363891</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V45" t="n">
-        <v>500.6242735046464</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="W45" t="n">
-        <v>500.6242735046464</v>
+        <v>518.4217842253022</v>
       </c>
       <c r="X45" t="n">
-        <v>292.7727732991136</v>
+        <v>518.4217842253022</v>
       </c>
       <c r="Y45" t="n">
-        <v>85.01247453415965</v>
+        <v>310.6614854603483</v>
       </c>
     </row>
     <row r="46">
@@ -7765,76 +7765,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C46" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D46" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E46" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F46" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G46" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H46" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I46" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J46" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K46" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L46" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M46" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N46" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O46" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P46" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q46" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R46" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S46" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T46" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U46" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V46" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W46" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X46" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y46" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
   </sheetData>
@@ -7968,13 +7968,13 @@
         <v>449.5135334928325</v>
       </c>
       <c r="N2" t="n">
-        <v>437.2903462297383</v>
+        <v>437.3469244119842</v>
       </c>
       <c r="O2" t="n">
         <v>380.8001812627454</v>
       </c>
       <c r="P2" t="n">
-        <v>321.7987081714826</v>
+        <v>321.7987081714824</v>
       </c>
       <c r="Q2" t="n">
         <v>212.3149906599047</v>
@@ -8038,25 +8038,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K3" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L3" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M3" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996773</v>
       </c>
       <c r="N3" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O3" t="n">
-        <v>303.7467114432442</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P3" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q3" t="n">
-        <v>139.9817740860215</v>
+        <v>186.7697506723097</v>
       </c>
       <c r="R3" t="n">
         <v>45.52166981132082</v>
@@ -8196,7 +8196,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K5" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L5" t="n">
         <v>417.6612145504504</v>
@@ -8211,7 +8211,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P5" t="n">
-        <v>321.7987081714826</v>
+        <v>321.7987081714824</v>
       </c>
       <c r="Q5" t="n">
         <v>212.3149906599047</v>
@@ -8275,22 +8275,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K6" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L6" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M6" t="n">
-        <v>383.1340339220183</v>
+        <v>359.8407857361377</v>
       </c>
       <c r="N6" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O6" t="n">
-        <v>185.8535934954385</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P6" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q6" t="n">
         <v>210.0772877358491</v>
@@ -8433,7 +8433,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711646</v>
       </c>
       <c r="L8" t="n">
         <v>417.6612145504504</v>
@@ -8518,13 +8518,13 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>359.81278530921</v>
+        <v>359.8407857361377</v>
       </c>
       <c r="N9" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O9" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P9" t="n">
         <v>318.4627686399372</v>
@@ -8679,7 +8679,7 @@
         <v>449.5135334928325</v>
       </c>
       <c r="N11" t="n">
-        <v>437.2903462297383</v>
+        <v>437.3469244119842</v>
       </c>
       <c r="O11" t="n">
         <v>380.8001812627454</v>
@@ -8755,16 +8755,16 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M12" t="n">
-        <v>383.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
-        <v>372.3417120833333</v>
+        <v>231.1529892133071</v>
       </c>
       <c r="O12" t="n">
-        <v>185.8535934954385</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P12" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q12" t="n">
         <v>210.0772877358491</v>
@@ -8922,7 +8922,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P14" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8989,16 +8989,16 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L15" t="n">
-        <v>229.6093331288462</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N15" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O15" t="n">
-        <v>383.5962444444444</v>
+        <v>233.6791982203443</v>
       </c>
       <c r="P15" t="n">
         <v>318.4627686399372</v>
@@ -9159,7 +9159,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P17" t="n">
-        <v>321.7421299892719</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9226,19 +9226,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
-        <v>370.8403453034592</v>
+        <v>369.8307175917693</v>
       </c>
       <c r="M18" t="n">
-        <v>197.6223334354527</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N18" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O18" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P18" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
         <v>139.9817740860215</v>
@@ -9396,7 +9396,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P20" t="n">
-        <v>321.7421299892939</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q20" t="n">
         <v>212.3149906599047</v>
@@ -9460,25 +9460,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L21" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>142.1340339220183</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
-        <v>303.8555545035439</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q21" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,22 +9697,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L24" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N24" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>382.5729051834858</v>
+        <v>312.5030352242461</v>
       </c>
       <c r="P24" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
         <v>139.9817740860215</v>
@@ -9855,10 +9855,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L26" t="n">
-        <v>417.6046363682045</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M26" t="n">
         <v>449.5135334928325</v>
@@ -9934,25 +9934,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>311.9985353972331</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N27" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>312.5053919605859</v>
       </c>
       <c r="P27" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10107,7 +10107,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P29" t="n">
-        <v>321.7421299893361</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10174,22 +10174,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L30" t="n">
-        <v>370.8403453034592</v>
+        <v>229.6373335557741</v>
       </c>
       <c r="M30" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N30" t="n">
-        <v>301.2062135585481</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10329,7 +10329,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L32" t="n">
         <v>417.6612145504504</v>
@@ -10411,22 +10411,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M33" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N33" t="n">
-        <v>372.3417120833333</v>
+        <v>371.3463732493024</v>
       </c>
       <c r="O33" t="n">
-        <v>360.2749958316361</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P33" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10581,7 +10581,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P35" t="n">
-        <v>321.7421299895137</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10645,19 +10645,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L36" t="n">
-        <v>370.8403453034592</v>
+        <v>243.2069195535496</v>
       </c>
       <c r="M36" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N36" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O36" t="n">
-        <v>382.5729051834858</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P36" t="n">
         <v>133.9744074143302</v>
@@ -10803,7 +10803,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
@@ -10885,19 +10885,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>370.8403453034592</v>
+        <v>185.3423563661624</v>
       </c>
       <c r="M39" t="n">
-        <v>382.1106946610595</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N39" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O39" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P39" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q39" t="n">
         <v>139.9817740860215</v>
@@ -11055,7 +11055,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P41" t="n">
-        <v>321.7421299893215</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11119,25 +11119,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>370.8403453034592</v>
+        <v>369.8307175917693</v>
       </c>
       <c r="M42" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N42" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O42" t="n">
-        <v>185.8535934954385</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P42" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q42" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11277,7 +11277,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K44" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L44" t="n">
         <v>417.6612145504504</v>
@@ -11356,22 +11356,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K45" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L45" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M45" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N45" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O45" t="n">
-        <v>185.8535934954385</v>
+        <v>360.302996258564</v>
       </c>
       <c r="P45" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q45" t="n">
         <v>210.0772877358491</v>
@@ -22504,10 +22504,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C2" t="n">
-        <v>153.0000917710075</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D2" t="n">
         <v>354.683041620683</v>
@@ -22549,28 +22549,28 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>10.3456529078365</v>
+        <v>10.3313640301775</v>
       </c>
       <c r="V2" t="n">
-        <v>327.7522584701349</v>
+        <v>225.4140313774462</v>
       </c>
       <c r="W2" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X2" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y2" t="n">
         <v>386.2379386560536</v>
@@ -22586,28 +22586,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C3" t="n">
-        <v>172.7084989883157</v>
+        <v>27.26179070270035</v>
       </c>
       <c r="D3" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -22631,22 +22631,22 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W3" t="n">
-        <v>247.1698863426223</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X3" t="n">
         <v>205.7729852034775</v>
@@ -22683,13 +22683,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I4" t="n">
-        <v>155.4504749272583</v>
+        <v>137.8921792844459</v>
       </c>
       <c r="J4" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -22704,13 +22704,13 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R4" t="n">
-        <v>132.9899077786024</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S4" t="n">
         <v>224.0165980369723</v>
@@ -22759,10 +22759,10 @@
         <v>415.302737515135</v>
       </c>
       <c r="H5" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810815</v>
       </c>
       <c r="I5" t="n">
-        <v>120.1281152310897</v>
+        <v>10.13979328157643</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -22786,19 +22786,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U5" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V5" t="n">
         <v>327.7522584701349</v>
@@ -22807,10 +22807,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X5" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y5" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783946</v>
       </c>
     </row>
     <row r="6">
@@ -22823,7 +22823,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C6" t="n">
-        <v>27.31724297911936</v>
+        <v>27.26179070270035</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -22917,7 +22917,7 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H7" t="n">
-        <v>162.2271725074396</v>
+        <v>29.04020492207155</v>
       </c>
       <c r="I7" t="n">
         <v>155.4504749272583</v>
@@ -22950,7 +22950,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S7" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T7" t="n">
         <v>227.9455894282815</v>
@@ -22990,19 +22990,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
-        <v>406.8760457417114</v>
+        <v>325.8706680867786</v>
       </c>
       <c r="G8" t="n">
-        <v>415.302737515135</v>
+        <v>174.2884486374761</v>
       </c>
       <c r="H8" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810815</v>
       </c>
       <c r="I8" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23023,22 +23023,22 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V8" t="n">
-        <v>225.4551947762062</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W8" t="n">
         <v>349.240968717413</v>
@@ -23057,13 +23057,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>26.57065165286144</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>21.08647536425201</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -23081,7 +23081,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -23157,13 +23157,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>155.4504749272583</v>
+        <v>137.8921792844459</v>
       </c>
       <c r="J10" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23184,7 +23184,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>44.10642379180146</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S10" t="n">
         <v>224.0165980369723</v>
@@ -23215,13 +23215,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858216</v>
       </c>
       <c r="C11" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933486</v>
       </c>
       <c r="D11" t="n">
-        <v>354.683041620683</v>
+        <v>142.397655977241</v>
       </c>
       <c r="E11" t="n">
         <v>381.9303700722618</v>
@@ -23260,22 +23260,22 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U11" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V11" t="n">
-        <v>225.4551947762062</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W11" t="n">
         <v>349.240968717413</v>
@@ -23284,7 +23284,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y11" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783946</v>
       </c>
     </row>
     <row r="12">
@@ -23318,7 +23318,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -23342,13 +23342,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>170.3657197299391</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -23357,10 +23357,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>247.9164776688802</v>
+        <v>10.68069428326061</v>
       </c>
       <c r="X12" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>205.6826957773044</v>
@@ -23379,7 +23379,7 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D13" t="n">
-        <v>131.0571773754</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E13" t="n">
         <v>146.4339626465692</v>
@@ -23397,10 +23397,10 @@
         <v>155.4504749272583</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23427,7 +23427,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T13" t="n">
-        <v>227.9455894282815</v>
+        <v>94.75862184291347</v>
       </c>
       <c r="U13" t="n">
         <v>286.3190293564909</v>
@@ -23452,28 +23452,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>382.7338416634806</v>
+        <v>180.4391552345834</v>
       </c>
       <c r="C14" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D14" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E14" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F14" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H14" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I14" t="n">
-        <v>8.193788784950669</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -23509,13 +23509,13 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U14" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W14" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X14" t="n">
         <v>369.731100678469</v>
@@ -23531,7 +23531,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C15" t="n">
         <v>172.7084989883157</v>
@@ -23582,7 +23582,7 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S15" t="n">
-        <v>61.85025267892691</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -23594,10 +23594,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X15" t="n">
-        <v>205.7729852034775</v>
+        <v>170.365719729939</v>
       </c>
       <c r="Y15" t="n">
         <v>205.6826957773044</v>
@@ -23610,7 +23610,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>179.8319801819373</v>
+        <v>46.64501259656927</v>
       </c>
       <c r="C16" t="n">
         <v>167.2468210986278</v>
@@ -23622,7 +23622,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F16" t="n">
-        <v>34.50357226344607</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
         <v>167.9909793584588</v>
@@ -23637,7 +23637,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23692,19 +23692,19 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C17" t="n">
-        <v>124.2728917710076</v>
+        <v>152.9875061275656</v>
       </c>
       <c r="D17" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E17" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F17" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G17" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H17" t="n">
         <v>339.4748021157671</v>
@@ -23752,13 +23752,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W17" t="n">
-        <v>136.9681687173786</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X17" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y17" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="18">
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,22 +23816,22 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>137.0224969565572</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>102.3965016096575</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X18" t="n">
         <v>205.7729852034775</v>
@@ -23892,7 +23892,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
         <v>177.2933913771695</v>
@@ -23904,10 +23904,10 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U19" t="n">
-        <v>239.2941050228173</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V19" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W19" t="n">
         <v>286.522998336591</v>
@@ -23926,31 +23926,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>170.4610416634246</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C20" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D20" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F20" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G20" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H20" t="n">
-        <v>339.4748021157671</v>
+        <v>149.1294050414824</v>
       </c>
       <c r="I20" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J20" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -23971,7 +23971,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>149.8691179411497</v>
@@ -23986,7 +23986,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V20" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
         <v>349.240968717413</v>
@@ -24005,22 +24005,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>102.6855239841052</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>112.2354442364965</v>
@@ -24029,7 +24029,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24059,16 +24059,16 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>197.477613413448</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X21" t="n">
         <v>205.7729852034775</v>
@@ -24084,7 +24084,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>179.8319801819373</v>
+        <v>46.64501259656927</v>
       </c>
       <c r="C22" t="n">
         <v>167.2468210986278</v>
@@ -24135,7 +24135,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S22" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T22" t="n">
         <v>227.9455894282815</v>
@@ -24172,22 +24172,22 @@
         <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>179.6482692868066</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F23" t="n">
-        <v>165.8760457417114</v>
+        <v>324.414848102618</v>
       </c>
       <c r="G23" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I23" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J23" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -24208,13 +24208,13 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>223.0958495641314</v>
@@ -24226,7 +24226,7 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W23" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X23" t="n">
         <v>369.731100678469</v>
@@ -24242,7 +24242,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>172.7084989883157</v>
@@ -24254,19 +24254,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
-        <v>34.32584428764393</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24293,22 +24293,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>83.22255503410561</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>205.6826957773044</v>
@@ -24321,7 +24321,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>132.8070558482637</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C25" t="n">
         <v>167.2468210986278</v>
@@ -24366,7 +24366,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
         <v>177.2933913771695</v>
@@ -24378,7 +24378,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U25" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24400,19 +24400,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C26" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D26" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E26" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F26" t="n">
-        <v>406.8760457417114</v>
+        <v>326.5413387258914</v>
       </c>
       <c r="G26" t="n">
         <v>415.302737515135</v>
@@ -24448,25 +24448,25 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T26" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>39.07285290783653</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W26" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X26" t="n">
-        <v>128.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y26" t="n">
         <v>386.2379386560536</v>
@@ -24482,7 +24482,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
         <v>147.4450655646388</v>
@@ -24500,7 +24500,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I27" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24530,25 +24530,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
-        <v>171.6831711038378</v>
+        <v>160.1517263084144</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>77.33955182272013</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X27" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="28">
@@ -24621,10 +24621,10 @@
         <v>252.137643323828</v>
       </c>
       <c r="W28" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X28" t="n">
-        <v>225.7096553890372</v>
+        <v>92.52268780366913</v>
       </c>
       <c r="Y28" t="n">
         <v>218.5846533520948</v>
@@ -24637,13 +24637,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>141.7338416634806</v>
+        <v>180.4391552345834</v>
       </c>
       <c r="C29" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D29" t="n">
-        <v>113.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E29" t="n">
         <v>381.9303700722618</v>
@@ -24682,7 +24682,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>149.8691179411497</v>
@@ -24694,7 +24694,7 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>39.07285290773908</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24706,7 +24706,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="30">
@@ -24716,10 +24716,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>147.4450655646388</v>
@@ -24728,16 +24728,16 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24767,25 +24767,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>237.1552763676522</v>
+        <v>144.45043018284</v>
       </c>
       <c r="X30" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -24804,7 +24804,7 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E31" t="n">
-        <v>146.4339626465692</v>
+        <v>13.24699506120115</v>
       </c>
       <c r="F31" t="n">
         <v>145.4210480229312</v>
@@ -24837,10 +24837,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
         <v>177.2933913771695</v>
@@ -24864,7 +24864,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y31" t="n">
-        <v>174.2811697535277</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="32">
@@ -24883,22 +24883,22 @@
         <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F32" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G32" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H32" t="n">
-        <v>339.4748021157671</v>
+        <v>127.189416472325</v>
       </c>
       <c r="I32" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -24922,25 +24922,25 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
-        <v>259.3937153300285</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
         <v>386.2379386560536</v>
@@ -24953,28 +24953,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>97.78184089914018</v>
       </c>
       <c r="H33" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
         <v>0.7465913262578567</v>
@@ -25004,7 +25004,7 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>135.9077653914357</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
         <v>200.1647286948216</v>
@@ -25016,7 +25016,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -25089,13 +25089,13 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U34" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X34" t="n">
         <v>225.7096553890372</v>
@@ -25111,13 +25111,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D35" t="n">
-        <v>142.4102416205423</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E35" t="n">
         <v>381.9303700722618</v>
@@ -25135,7 +25135,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J35" t="n">
-        <v>11.94928935448171</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -25171,16 +25171,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
-        <v>327.7522584701349</v>
+        <v>115.4668728266929</v>
       </c>
       <c r="W35" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X35" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y35" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="36">
@@ -25190,10 +25190,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
-        <v>22.33474951932527</v>
+        <v>89.30758094638082</v>
       </c>
       <c r="D36" t="n">
         <v>147.4450655646388</v>
@@ -25214,7 +25214,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25250,10 +25250,10 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X36" t="n">
         <v>205.7729852034775</v>
@@ -25284,7 +25284,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.9909793584588</v>
+        <v>34.80401177309074</v>
       </c>
       <c r="H37" t="n">
         <v>162.2271725074396</v>
@@ -25329,7 +25329,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V37" t="n">
-        <v>118.95067573846</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W37" t="n">
         <v>286.522998336591</v>
@@ -25348,25 +25348,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>141.7338416634806</v>
+        <v>170.4484560200386</v>
       </c>
       <c r="C38" t="n">
-        <v>124.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D38" t="n">
-        <v>152.4009408352277</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H38" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I38" t="n">
         <v>210.4758895704059</v>
@@ -25393,7 +25393,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
         <v>149.8691179411497</v>
@@ -25433,13 +25433,13 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
-        <v>140.3151268879898</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F39" t="n">
-        <v>145.0692123933839</v>
+        <v>120.0043563196803</v>
       </c>
       <c r="G39" t="n">
         <v>137.3435171632106</v>
@@ -25475,13 +25475,13 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -25493,10 +25493,10 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X39" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -25585,25 +25585,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>288.3502291907927</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C41" t="n">
-        <v>124.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D41" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G41" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H41" t="n">
-        <v>339.4748021157671</v>
+        <v>127.189416472325</v>
       </c>
       <c r="I41" t="n">
         <v>210.4758895704059</v>
@@ -25633,10 +25633,10 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T41" t="n">
         <v>223.0958495641314</v>
@@ -25664,10 +25664,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
         <v>147.4450655646388</v>
@@ -25682,10 +25682,10 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
-        <v>17.80323203313432</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25721,19 +25721,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>176.6302781386796</v>
       </c>
     </row>
     <row r="43">
@@ -25794,13 +25794,13 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S43" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T43" t="n">
         <v>227.9455894282815</v>
       </c>
       <c r="U43" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25822,7 +25822,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C44" t="n">
         <v>365.2728917710076</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H44" t="n">
-        <v>256.5377088418676</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J44" t="n">
         <v>11.94928935461252</v>
@@ -25870,25 +25870,25 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S44" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T44" t="n">
-        <v>223.0958495641314</v>
+        <v>20.80116313523413</v>
       </c>
       <c r="U44" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V44" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W44" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X44" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y44" t="n">
         <v>386.2379386560536</v>
@@ -25901,16 +25901,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>166.5331836498673</v>
+        <v>50.77514371154889</v>
       </c>
       <c r="C45" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E45" t="n">
-        <v>92.56993066658289</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F45" t="n">
         <v>145.0692123933839</v>
@@ -25955,19 +25955,19 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T45" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W45" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -26037,7 +26037,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U46" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26046,7 +26046,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X46" t="n">
-        <v>92.52268780366913</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y46" t="n">
         <v>218.5846533520948</v>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>473607.8178471013</v>
+        <v>473617.4616593693</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>473607.8178471011</v>
+        <v>473617.4616593693</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>473607.8178471011</v>
+        <v>473617.4616593693</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>473607.817847101</v>
+        <v>473617.4616593693</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>473607.8178471011</v>
+        <v>473617.4616593693</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>473607.817847105</v>
+        <v>473617.4616593693</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>473607.8178471075</v>
+        <v>473617.4616593695</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>473607.8178471011</v>
+        <v>473617.4616593693</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>473607.8178471012</v>
+        <v>473617.4616593693</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>473607.8178471122</v>
+        <v>473617.4616593695</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>473607.8178471013</v>
+        <v>473617.4616593695</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>473607.8178471321</v>
+        <v>473617.4616593693</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>473607.8178471011</v>
+        <v>473617.4616593695</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>473607.8178471107</v>
+        <v>473617.4616593693</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>473607.8178471011</v>
+        <v>473617.4616593695</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>116310.1029597295</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="C2" t="n">
-        <v>116310.1029597296</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="D2" t="n">
-        <v>116310.1029597296</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="E2" t="n">
-        <v>116310.1029597296</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="F2" t="n">
-        <v>116310.1029597295</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="G2" t="n">
-        <v>116310.1029597305</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="H2" t="n">
-        <v>116310.1029597311</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="I2" t="n">
-        <v>116310.1029597296</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="J2" t="n">
-        <v>116310.1029597296</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="K2" t="n">
-        <v>116310.1029597323</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="L2" t="n">
-        <v>116310.1029597296</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="M2" t="n">
-        <v>116310.1029597371</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="N2" t="n">
-        <v>116310.1029597296</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="O2" t="n">
-        <v>116310.1029597319</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="P2" t="n">
-        <v>116310.1029597296</v>
+        <v>116312.4707719327</v>
       </c>
     </row>
     <row r="3">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80764.643</v>
+        <v>80769.43153154771</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26337,7 +26337,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>63056.204</v>
+        <v>63059.94259910621</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8546.928152079201</v>
+        <v>6716.703256796494</v>
       </c>
       <c r="C4" t="n">
-        <v>8546.928152079201</v>
+        <v>6716.703256796493</v>
       </c>
       <c r="D4" t="n">
-        <v>8546.928152079201</v>
+        <v>6716.703256796493</v>
       </c>
       <c r="E4" t="n">
-        <v>8546.928152079201</v>
+        <v>6716.703256796494</v>
       </c>
       <c r="F4" t="n">
-        <v>8546.928152079199</v>
+        <v>6716.703256796494</v>
       </c>
       <c r="G4" t="n">
-        <v>8546.928152079276</v>
+        <v>6716.703256796494</v>
       </c>
       <c r="H4" t="n">
-        <v>8546.928152079321</v>
+        <v>6716.703256796494</v>
       </c>
       <c r="I4" t="n">
-        <v>8546.928152079201</v>
+        <v>6716.703256796494</v>
       </c>
       <c r="J4" t="n">
-        <v>8546.928152079201</v>
+        <v>6716.703256796494</v>
       </c>
       <c r="K4" t="n">
-        <v>8546.92815207941</v>
+        <v>6716.703256796494</v>
       </c>
       <c r="L4" t="n">
-        <v>8546.928152079201</v>
+        <v>6716.703256796494</v>
       </c>
       <c r="M4" t="n">
-        <v>8546.928152079785</v>
+        <v>6716.703256796494</v>
       </c>
       <c r="N4" t="n">
-        <v>8546.928152079199</v>
+        <v>6716.703256796494</v>
       </c>
       <c r="O4" t="n">
-        <v>8546.928152079381</v>
+        <v>6716.703256796494</v>
       </c>
       <c r="P4" t="n">
-        <v>8546.928152079201</v>
+        <v>6716.703256796494</v>
       </c>
     </row>
     <row r="5">
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376166</v>
       </c>
       <c r="C5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376166</v>
       </c>
       <c r="D5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376166</v>
       </c>
       <c r="E5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="F5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="G5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="P5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-21281.86819234966</v>
+        <v>-19454.93278017321</v>
       </c>
       <c r="C6" t="n">
-        <v>59482.77480765042</v>
+        <v>61314.4987513745</v>
       </c>
       <c r="D6" t="n">
-        <v>59482.77480765041</v>
+        <v>61314.49875137454</v>
       </c>
       <c r="E6" t="n">
-        <v>93110.37480765037</v>
+        <v>94942.09875137452</v>
       </c>
       <c r="F6" t="n">
-        <v>93110.37480765034</v>
+        <v>94942.09875137449</v>
       </c>
       <c r="G6" t="n">
-        <v>93110.37480765126</v>
+        <v>94942.09875137451</v>
       </c>
       <c r="H6" t="n">
-        <v>93110.37480765181</v>
+        <v>94942.09875137453</v>
       </c>
       <c r="I6" t="n">
-        <v>93110.37480765035</v>
+        <v>94942.09875137453</v>
       </c>
       <c r="J6" t="n">
-        <v>30054.17080765036</v>
+        <v>31882.15615226831</v>
       </c>
       <c r="K6" t="n">
-        <v>93110.37480765289</v>
+        <v>94942.09875137449</v>
       </c>
       <c r="L6" t="n">
-        <v>93110.37480765041</v>
+        <v>94942.09875137455</v>
       </c>
       <c r="M6" t="n">
-        <v>93110.37480765735</v>
+        <v>94942.09875137452</v>
       </c>
       <c r="N6" t="n">
-        <v>93110.37480765035</v>
+        <v>94942.09875137452</v>
       </c>
       <c r="O6" t="n">
-        <v>93110.37480765254</v>
+        <v>94942.09875137452</v>
       </c>
       <c r="P6" t="n">
-        <v>93110.37480765038</v>
+        <v>94942.09875137453</v>
       </c>
     </row>
   </sheetData>
@@ -26727,49 +26727,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="C4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="D4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="E4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="F4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
   </sheetData>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26910,31 +26910,31 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27185,7 +27185,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34623,13 +34623,13 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N2" t="n">
-        <v>207.8772826331474</v>
+        <v>207.9338608153932</v>
       </c>
       <c r="O2" t="n">
         <v>150.7019698410586</v>
       </c>
       <c r="P2" t="n">
-        <v>90.5657124162131</v>
+        <v>90.56571241621288</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -34693,25 +34693,25 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="N3" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="O3" t="n">
-        <v>161.1504669987997</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P3" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>46.78797658628819</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -34851,7 +34851,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L5" t="n">
         <v>181.8947995804632</v>
@@ -34866,7 +34866,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P5" t="n">
-        <v>90.5657124162131</v>
+        <v>90.56571241621288</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -34930,22 +34930,22 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>241</v>
+        <v>217.7067518141194</v>
       </c>
       <c r="N6" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="O6" t="n">
-        <v>43.25734905099405</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q6" t="n">
         <v>70.09551364982758</v>
@@ -35088,7 +35088,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>103.9989833439383</v>
+        <v>104.055561526184</v>
       </c>
       <c r="L8" t="n">
         <v>181.8947995804632</v>
@@ -35173,13 +35173,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>217.6787513871916</v>
+        <v>217.7067518141194</v>
       </c>
       <c r="N9" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="O9" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P9" t="n">
         <v>184.4883612256069</v>
@@ -35334,7 +35334,7 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N11" t="n">
-        <v>207.8772826331474</v>
+        <v>207.9338608153932</v>
       </c>
       <c r="O11" t="n">
         <v>150.7019698410586</v>
@@ -35410,16 +35410,16 @@
         <v>232.285965523585</v>
       </c>
       <c r="M12" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>241</v>
+        <v>99.81127712997385</v>
       </c>
       <c r="O12" t="n">
-        <v>43.25734905099405</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q12" t="n">
         <v>70.09551364982758</v>
@@ -35577,7 +35577,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P14" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35644,16 +35644,16 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L15" t="n">
-        <v>91.05495334897203</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O15" t="n">
-        <v>241</v>
+        <v>91.0829537758999</v>
       </c>
       <c r="P15" t="n">
         <v>184.4883612256069</v>
@@ -35814,7 +35814,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P17" t="n">
-        <v>90.50913423400232</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35881,19 +35881,19 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>232.285965523585</v>
+        <v>231.276337811895</v>
       </c>
       <c r="M18" t="n">
-        <v>55.48829951343433</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N18" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O18" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P18" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -36051,7 +36051,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P20" t="n">
-        <v>90.50913423402436</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36115,25 +36115,25 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L21" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
-        <v>169.8811470892137</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q21" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,22 +36352,22 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L24" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N24" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>239.9766607390413</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -36513,7 +36513,7 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
-        <v>181.8382213982173</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M26" t="n">
         <v>219.1673002655598</v>
@@ -36589,25 +36589,25 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>169.9091475161414</v>
       </c>
       <c r="P27" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36753,7 +36753,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M29" t="n">
-        <v>219.1673002655598</v>
+        <v>219.1673002655597</v>
       </c>
       <c r="N29" t="n">
         <v>207.9338608153932</v>
@@ -36762,7 +36762,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P29" t="n">
-        <v>90.50913423406662</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36829,22 +36829,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L30" t="n">
-        <v>232.285965523585</v>
+        <v>91.0829537758999</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N30" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36984,7 +36984,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L32" t="n">
         <v>181.8947995804632</v>
@@ -37066,22 +37066,22 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M33" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N33" t="n">
-        <v>241</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="O33" t="n">
-        <v>217.6787513871916</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P33" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37236,7 +37236,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P35" t="n">
-        <v>90.50913423424416</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37300,19 +37300,19 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L36" t="n">
-        <v>232.285965523585</v>
+        <v>104.6525397736754</v>
       </c>
       <c r="M36" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N36" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O36" t="n">
-        <v>239.9766607390413</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -37458,7 +37458,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L38" t="n">
         <v>181.8947995804632</v>
@@ -37540,19 +37540,19 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>232.285965523585</v>
+        <v>46.78797658628819</v>
       </c>
       <c r="M39" t="n">
-        <v>239.9766607390412</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N39" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O39" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37710,7 +37710,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P41" t="n">
-        <v>90.50913423405193</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37774,25 +37774,25 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>232.285965523585</v>
+        <v>231.276337811895</v>
       </c>
       <c r="M42" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N42" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O42" t="n">
-        <v>43.25734905099405</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37932,7 +37932,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L44" t="n">
         <v>181.8947995804632</v>
@@ -38011,22 +38011,22 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N45" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O45" t="n">
-        <v>43.25734905099405</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q45" t="n">
         <v>70.09551364982758</v>
